--- a/public/template_excel/DATA PEGAWAI NON ASN.xlsx
+++ b/public/template_excel/DATA PEGAWAI NON ASN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hasbee\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\WORK\simdatuk-dev\public\template_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,13 +13,22 @@
   </bookViews>
   <sheets>
     <sheet name="Data Pegawai" sheetId="1" r:id="rId1"/>
-    <sheet name="Pendidikan" sheetId="2" r:id="rId2"/>
-    <sheet name="Keluarga" sheetId="13" r:id="rId3"/>
-    <sheet name="Cuti" sheetId="14" r:id="rId4"/>
-    <sheet name="Catatan" sheetId="15" r:id="rId5"/>
-    <sheet name="Hasil Assessment" sheetId="16" r:id="rId6"/>
-    <sheet name="Hasil Uji Kompetensi" sheetId="17" r:id="rId7"/>
-    <sheet name="Hasil Talent Pool" sheetId="18" r:id="rId8"/>
+    <sheet name="Riwayat Pendidikan" sheetId="2" r:id="rId2"/>
+    <sheet name="Riwayat Jabatan" sheetId="4" r:id="rId3"/>
+    <sheet name="Riwayat Golongan" sheetId="3" r:id="rId4"/>
+    <sheet name="Riwayat Pelatihan Struktural" sheetId="6" r:id="rId5"/>
+    <sheet name="Riwayat Pelatihan Fungsional" sheetId="7" r:id="rId6"/>
+    <sheet name="Riwayat Pelatihan Teknis" sheetId="8" r:id="rId7"/>
+    <sheet name="Riwayat Penghargaan" sheetId="9" r:id="rId8"/>
+    <sheet name="Riwayat SKP" sheetId="10" r:id="rId9"/>
+    <sheet name="Penilaian Prestasi Kerja" sheetId="11" r:id="rId10"/>
+    <sheet name="Riwayat Hukuman Disiplin" sheetId="12" r:id="rId11"/>
+    <sheet name="Riwayat Keluarga" sheetId="13" r:id="rId12"/>
+    <sheet name="Riwayat Cuti" sheetId="14" r:id="rId13"/>
+    <sheet name="Riwayat Catatan" sheetId="15" r:id="rId14"/>
+    <sheet name="Hasil Assessment" sheetId="16" r:id="rId15"/>
+    <sheet name="Hasil Uji Kompetensi" sheetId="17" r:id="rId16"/>
+    <sheet name="Hasil Talent Pool" sheetId="18" r:id="rId17"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -30,49 +39,67 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Windows User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+* Masukkan Jabatan dari Hirarki tertinggi
+* Pisahkan Hirarki menggunakan tanda '&gt;'
+Contoh 1 : Misal Jabatan 'Arsiparis'
+Kepala Sekretariat Wakil Presiden&gt;Deputi Bidang Administrasi&gt;Kepala Biro Umum&gt;Arsiparis
+Contoh 2 : Misal Jabatan 'Staf Khusus Wakil Presiden (Bidang Umum)'
+Staf Khusus Wakil Presiden&gt;Staf Khusus Wakil Presiden (Bidang Umum)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
-  <si>
-    <t>Nama</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
   <si>
     <t>Golongan</t>
   </si>
   <si>
-    <t>NIP</t>
-  </si>
-  <si>
     <t>NRP</t>
   </si>
   <si>
-    <t>Tempat Lahir</t>
-  </si>
-  <si>
-    <t>Agama</t>
-  </si>
-  <si>
-    <t>Tingkat</t>
-  </si>
-  <si>
-    <t>Nama Sekolah</t>
-  </si>
-  <si>
     <t>Fakultas</t>
   </si>
   <si>
     <t>Jurusan</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Tahun Lulus</t>
-  </si>
-  <si>
-    <t>TMT Golongan</t>
-  </si>
-  <si>
-    <t>Tanggal Lahir</t>
+    <t>SK Golongan</t>
+  </si>
+  <si>
+    <t>Jenis SK Golongan</t>
+  </si>
+  <si>
+    <t>No. SK Golongan</t>
   </si>
   <si>
     <t>Nama Gelar Depan</t>
@@ -81,137 +108,338 @@
     <t>Nama Gelar Belakang</t>
   </si>
   <si>
-    <t>Jenis Kelamin</t>
-  </si>
-  <si>
-    <t>Status Perkawinan</t>
-  </si>
-  <si>
-    <t>Jenis Pegawai</t>
-  </si>
-  <si>
-    <t>Jenis Outsourcing</t>
+    <t>Jabatan</t>
+  </si>
+  <si>
+    <t>TMT Eselon</t>
+  </si>
+  <si>
+    <t>Tahun</t>
+  </si>
+  <si>
+    <t>No Karpeg</t>
+  </si>
+  <si>
+    <t>NPWP</t>
+  </si>
+  <si>
+    <t>Alamat Tempat Tinggal Saat Ini</t>
+  </si>
+  <si>
+    <t>No Telepon Rumah</t>
+  </si>
+  <si>
+    <t>No HP</t>
+  </si>
+  <si>
+    <t>Alamat Kantor</t>
+  </si>
+  <si>
+    <t>No Telepon Kantor</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Keterangan Sekolah</t>
+  </si>
+  <si>
+    <t>Rumpun</t>
+  </si>
+  <si>
+    <t>Jenjang Jabatan</t>
+  </si>
+  <si>
+    <t>Keterangan Jabatan</t>
+  </si>
+  <si>
+    <t>SK Jabatan</t>
+  </si>
+  <si>
+    <t>Jenis SK Jabatan</t>
+  </si>
+  <si>
+    <t>No SK Jabatan</t>
+  </si>
+  <si>
+    <t>Tanggal SK Jabatan</t>
+  </si>
+  <si>
+    <t>TMT Selesai</t>
+  </si>
+  <si>
+    <t>SK Selesai</t>
+  </si>
+  <si>
+    <t>Jenis SK Selesai</t>
+  </si>
+  <si>
+    <t>No SK Selesai</t>
+  </si>
+  <si>
+    <t>Tanggal SK Selesai</t>
+  </si>
+  <si>
+    <t>Tanggal SK Golongan</t>
+  </si>
+  <si>
+    <t>Keterangan Golongan</t>
+  </si>
+  <si>
+    <t>Status Golongan</t>
+  </si>
+  <si>
+    <t>Jenjang</t>
+  </si>
+  <si>
+    <t>Durasi Pelatihan (Hari)</t>
+  </si>
+  <si>
+    <t>Penyelenggara</t>
+  </si>
+  <si>
+    <t>Keterangan Penghargaan</t>
+  </si>
+  <si>
+    <t>Tahun SK</t>
+  </si>
+  <si>
+    <t>Instansi Pemberi Penghargaan</t>
+  </si>
+  <si>
+    <t>Tanggal Terima</t>
+  </si>
+  <si>
+    <t>Keterangan</t>
+  </si>
+  <si>
+    <t>No. SK Hukuman Disiplin</t>
+  </si>
+  <si>
+    <t>Tanggal SK Hukuman Disiplin</t>
+  </si>
+  <si>
+    <t>Pejabat Berwenang</t>
+  </si>
+  <si>
+    <t>Nama Pejabat Berwenang</t>
+  </si>
+  <si>
+    <t>Uraian</t>
+  </si>
+  <si>
+    <t>Nama Bapak</t>
+  </si>
+  <si>
+    <t>Nama Ibu</t>
+  </si>
+  <si>
+    <t>Jenis Pekerjaan</t>
+  </si>
+  <si>
+    <t>Keterangan Pekerjaan</t>
+  </si>
+  <si>
+    <t>Urut Keluarga</t>
+  </si>
+  <si>
+    <t>No Karisu</t>
+  </si>
+  <si>
+    <t>NIK *</t>
+  </si>
+  <si>
+    <t>Jenis Hukuman *</t>
+  </si>
+  <si>
+    <t>Tanggal Hukuman Disiplin *</t>
+  </si>
+  <si>
+    <t>Nama Riwayat Hukuman Disiplin *</t>
+  </si>
+  <si>
+    <t>Bulan Periode Input Riwayat *</t>
+  </si>
+  <si>
+    <t>Tahun Periode Input Riwayat *</t>
+  </si>
+  <si>
+    <t>Nama *</t>
+  </si>
+  <si>
+    <t>NIP *</t>
+  </si>
+  <si>
+    <t>Tempat Lahir *</t>
+  </si>
+  <si>
+    <t>Tanggal Lahir *</t>
+  </si>
+  <si>
+    <t>Agama *</t>
+  </si>
+  <si>
+    <t>Jenis Kelamin *</t>
+  </si>
+  <si>
+    <t>Status Perkawinan *</t>
+  </si>
+  <si>
+    <t>Golongan *</t>
+  </si>
+  <si>
+    <t>TMT Golongan *</t>
+  </si>
+  <si>
+    <t>Instansi Induk *</t>
+  </si>
+  <si>
+    <t>Tingkat *</t>
+  </si>
+  <si>
+    <t>Nama Sekolah/Universitas *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tahun Lulus * </t>
+  </si>
+  <si>
+    <t>Status Pegawai *</t>
+  </si>
+  <si>
+    <t>No NIK *</t>
+  </si>
+  <si>
+    <t>Komplek *</t>
+  </si>
+  <si>
+    <t>Nama Sekolah *</t>
+  </si>
+  <si>
+    <t>Status *</t>
+  </si>
+  <si>
+    <t>Tahun Lulus *</t>
+  </si>
+  <si>
+    <t>No Kartu Keluarga *</t>
+  </si>
+  <si>
+    <t>Nama Anggota Keluarga *</t>
+  </si>
+  <si>
+    <t>Hubungan Keluarga *</t>
+  </si>
+  <si>
+    <t>Pendidikan *</t>
+  </si>
+  <si>
+    <t>Catatan *</t>
+  </si>
+  <si>
+    <t>Hasil *</t>
+  </si>
+  <si>
+    <t>Nama Riwayat Jabatan *</t>
+  </si>
+  <si>
+    <t>Jabatan *</t>
+  </si>
+  <si>
+    <t>TMT Menjabat *</t>
+  </si>
+  <si>
+    <t>Nama Riwayat Golongan *</t>
+  </si>
+  <si>
+    <t>Nama Riwayat PPK *</t>
+  </si>
+  <si>
+    <t>Periode PPK *</t>
+  </si>
+  <si>
+    <t>Nilai Prestasi Kerja *</t>
+  </si>
+  <si>
+    <t>Nama Riwayat SKP *</t>
+  </si>
+  <si>
+    <t>Periode Penilaian *</t>
+  </si>
+  <si>
+    <t>Rating Perilaku Kerja *</t>
+  </si>
+  <si>
+    <t>Predikat Kinerja Pegawai *</t>
+  </si>
+  <si>
+    <t>Capaian Kinerja Organisasi *</t>
+  </si>
+  <si>
+    <t>Nama Penghargaan *</t>
+  </si>
+  <si>
+    <t>Kontak Darurat (Nama, Nomor Handphone, Hubungan dengan pegawai) *</t>
+  </si>
+  <si>
+    <t>No KK *</t>
   </si>
   <si>
     <t>Eselon</t>
   </si>
   <si>
-    <t>TMT Eselon</t>
-  </si>
-  <si>
-    <t>Instansi Induk</t>
-  </si>
-  <si>
-    <t>Nama Sekolah/Universitas</t>
-  </si>
-  <si>
-    <t>No Karpeg</t>
-  </si>
-  <si>
-    <t>NPWP</t>
-  </si>
-  <si>
-    <t>Status Pegawai</t>
-  </si>
-  <si>
-    <t>No KK</t>
-  </si>
-  <si>
-    <t>No NIK</t>
-  </si>
-  <si>
-    <t>Komplek</t>
-  </si>
-  <si>
-    <t>Alamat Tempat Tinggal Saat Ini</t>
-  </si>
-  <si>
-    <t>No Telepon Rumah</t>
-  </si>
-  <si>
-    <t>No HP</t>
-  </si>
-  <si>
-    <t>Alamat Kantor</t>
-  </si>
-  <si>
-    <t>No Telepon Kantor</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Kontak Darurat (Nama, Nomor Handphone, Hubungan dengan pegawai)</t>
-  </si>
-  <si>
-    <t>Keterangan Sekolah</t>
-  </si>
-  <si>
-    <t>Penyelenggara</t>
-  </si>
-  <si>
-    <t>Keterangan</t>
-  </si>
-  <si>
-    <t>No Kartu Keluarga</t>
-  </si>
-  <si>
-    <t>Nama Anggota Keluarga</t>
-  </si>
-  <si>
-    <t>Nama Bapak</t>
-  </si>
-  <si>
-    <t>Nama Ibu</t>
-  </si>
-  <si>
-    <t>Hubungan Keluarga</t>
-  </si>
-  <si>
-    <t>Pendidikan</t>
-  </si>
-  <si>
-    <t>Jenis Pekerjaan</t>
-  </si>
-  <si>
-    <t>Keterangan Pekerjaan</t>
-  </si>
-  <si>
-    <t>Urut Keluarga</t>
-  </si>
-  <si>
-    <t>No Cuti</t>
-  </si>
-  <si>
-    <t>Tanggal</t>
-  </si>
-  <si>
-    <t>Catatan</t>
-  </si>
-  <si>
-    <t>Hasil</t>
-  </si>
-  <si>
-    <t>NIK</t>
-  </si>
-  <si>
-    <t>No Karisu</t>
-  </si>
-  <si>
-    <t>Tanggal Awal Cuti</t>
-  </si>
-  <si>
-    <t>Tanggal Akhir Cuti</t>
-  </si>
-  <si>
-    <t>Jenis Cuti</t>
+    <t>Tingkat Pendidikan Terakhir*</t>
+  </si>
+  <si>
+    <t>Email Dinas</t>
+  </si>
+  <si>
+    <t>Tanggal Awal Cuti *</t>
+  </si>
+  <si>
+    <t>Tanggal Akhir Cuti *</t>
+  </si>
+  <si>
+    <t>Jenis Cuti *</t>
+  </si>
+  <si>
+    <t>No Cuti *</t>
+  </si>
+  <si>
+    <t>Keterangan *</t>
+  </si>
+  <si>
+    <t>Tanggal *</t>
+  </si>
+  <si>
+    <t>Nama Diklat *</t>
+  </si>
+  <si>
+    <t>No Surat Perintah *</t>
+  </si>
+  <si>
+    <t>Tanggal Pelaksanaan *</t>
+  </si>
+  <si>
+    <t>No SK Penghargaan *</t>
+  </si>
+  <si>
+    <t>Jenis SK *</t>
+  </si>
+  <si>
+    <t>Tanggal SK *</t>
+  </si>
+  <si>
+    <t>Jenis Perbantuan *</t>
+  </si>
+  <si>
+    <t>Tanggal Mulai Bekerja *</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,6 +462,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -545,229 +786,316 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="33.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="24" style="1" customWidth="1"/>
-    <col min="19" max="19" width="27.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="67" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="25.28515625" style="1" customWidth="1"/>
-    <col min="34" max="34" width="73.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="14" width="19.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="21.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="33.140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="30.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="25.28515625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="73.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="AG2" s="4"/>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="AG3" s="4"/>
+      <c r="AJ1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4"/>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="25" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9.140625" style="1"/>
@@ -775,55 +1103,55 @@
   <sheetData>
     <row r="1" spans="1:17" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -832,14 +1160,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="29.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" style="1" customWidth="1"/>
@@ -849,22 +1177,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +1200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -884,10 +1212,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -895,7 +1223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -903,20 +1231,20 @@
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>38</v>
@@ -927,7 +1255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -942,13 +1270,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>38</v>
@@ -959,7 +1287,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -967,23 +1295,473 @@
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="23.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="53.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="23.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="54" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="23.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/public/template_excel/DATA PEGAWAI NON ASN.xlsx
+++ b/public/template_excel/DATA PEGAWAI NON ASN.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" firstSheet="7" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Data Pegawai" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="119">
   <si>
     <t>Golongan</t>
   </si>
@@ -252,9 +252,6 @@
     <t>Jenis Hukuman *</t>
   </si>
   <si>
-    <t>Tanggal Hukuman Disiplin *</t>
-  </si>
-  <si>
     <t>Nama Riwayat Hukuman Disiplin *</t>
   </si>
   <si>
@@ -433,6 +430,12 @@
   </si>
   <si>
     <t>Tanggal Mulai Bekerja *</t>
+  </si>
+  <si>
+    <t>Tanggal Awal Hukuman Disiplin *</t>
+  </si>
+  <si>
+    <t>Tanggal Akhir Hukuman Disiplin *</t>
   </si>
 </sst>
 </file>
@@ -828,7 +831,7 @@
   <sheetData>
     <row r="1" spans="1:37" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>7</v>
@@ -837,61 +840,61 @@
         <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="Q1" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="W1" s="2" t="s">
         <v>12</v>
@@ -903,16 +906,16 @@
         <v>13</v>
       </c>
       <c r="Z1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AA1" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="AD1" s="2" t="s">
         <v>14</v>
@@ -933,10 +936,10 @@
         <v>19</v>
       </c>
       <c r="AJ1" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AK1" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
@@ -971,22 +974,22 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>43</v>
@@ -999,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -1011,20 +1014,21 @@
     <col min="7" max="7" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="34.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>55</v>
@@ -1045,19 +1049,22 @@
         <v>45</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1106,25 +1113,25 @@
         <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>49</v>
@@ -1133,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>51</v>
@@ -1145,7 +1152,7 @@
         <v>52</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>16</v>
@@ -1180,19 +1187,19 @@
         <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1215,7 +1222,7 @@
         <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1241,10 +1248,10 @@
         <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>38</v>
@@ -1273,10 +1280,10 @@
         <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>38</v>
@@ -1305,10 +1312,10 @@
         <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>38</v>
@@ -1340,10 +1347,10 @@
         <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1352,10 +1359,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>20</v>
@@ -1395,19 +1402,19 @@
   <sheetData>
     <row r="1" spans="1:18" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>21</v>
@@ -1419,7 +1426,7 @@
         <v>23</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>24</v>
@@ -1476,22 +1483,22 @@
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
@@ -1536,22 +1543,22 @@
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>37</v>
@@ -1585,22 +1592,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>36</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>37</v>
@@ -1633,19 +1640,19 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>37</v>
@@ -1680,25 +1687,25 @@
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>40</v>
@@ -1737,16 +1744,16 @@
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>11</v>
@@ -1755,13 +1762,13 @@
         <v>55</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/public/template_excel/DATA PEGAWAI NON ASN.xlsx
+++ b/public/template_excel/DATA PEGAWAI NON ASN.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" firstSheet="7" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Data Pegawai" sheetId="1" r:id="rId1"/>
@@ -45,6 +45,127 @@
     <author>Windows User</author>
   </authors>
   <commentList>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Agama</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+- Islam
+- Kristen
+- Katolik
+- Hindu
+- Budha
+- Konghucu</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jenis Kelamin</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+- Perempuan
+- Laki-laki</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Status Perkawinan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+- Belum Menikah
+- Menikah
+- Cerai
+- Janda
+- Duda</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jenis Perbantuan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+STAF KHUSUS
+ASISTEN / STAF
+ASISTEN STAF KHUSUS
+SEKRETARIAT PADA STAF KHUSUS
+ANGGOTA TIM AHLI
+TNI/POLRI (TIM AJUDAN)
+TNI/POLRI (TIM DOKTER PRIBADI)
+TNI/POLRI (PENGEMUDI)
+PEMBANTU ASISTEN STAF KHUSUS
+STAF PADA SESPRI
+TPPS
+TNP2K
+TNI/POLRI (PROTOKOL)
+SESPRI
+STAF KERUMAHTANGGAAN
+STAF ISTRI PRESIDEN</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <r>
@@ -55,7 +176,8 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>Windows User:</t>
+          <t xml:space="preserve">Jabatan
+</t>
         </r>
         <r>
           <rPr>
@@ -74,12 +196,1478 @@
         </r>
       </text>
     </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Golongan
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Pembina Utama
+Pembina Utama Madya
+Pembina Utama Muda
+Pembina Tingkat I
+Pembina
+Penata Tingkat I
+Penata
+Penata Muda Tingkat I
+Penata Muda
+Pengatur Tingkat I
+Pengatur
+Pengatur Muda Tingkat I
+Pengatur Muda
+Juru Tingkat I
+Juru
+Juru Muda Tingkat I
+Juru Muda
+Golongan XVII
+Golongan XVI
+Golongan XV
+Golongan XIV
+Golongan XIII
+Golongan XII
+Golongan XI
+Golongan X
+Golongan IX
+Golongan VIII
+Golongan VII
+Golongan VI
+Golongan V
+Golongan IV
+Golongan III
+Golongan II
+Golongan </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eselon
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Eselon I
+Eselon II
+Eselon III
+Eselon IV
+Ahli Utama
+Ahli Madya
+Ahli Muda
+Ahli Pertama
+Pelaksana
+Penyelia
+Mahir
+Terampil
+Pemula</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Instansi Induk</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Kementerian Sekretariat Negara
+Kementerian Perindustrian dan Perdagangan
+Kementerian Perdagangan
+Kementerian Riset, Teknologi dan Pendidikan Tinggi
+Kementerian Luar Negeri
+Kementerian Koordinator Bidang Pembangunan Manusia dan Kebudayaan
+Kementerian Keuangan
+Kementerian Hukum dan HAM
+Kementerian Dalam Negeri
+Kementerian PPN/ Bappenas
+Kementerian Sosial
+Departemen Pekerjaan Umum
+Departemen Luar Negeri
+Departemen Dalam Negeri
+Badan Pengawas Keuangan dan Pembangunan (BPKP)
+Lembaga Ilmu Pengetahuan Indonesia (LIPI)
+Perpustakaan Nasional
+Lembaga Administrasi Negara (LAN)
+Badan Kepegawaian Negara (BKN)
+Pemerintah Kota Surabaya Provinsi Jawa Timur
+Sekretariat Militer Presiden
+Markas Besar TNI
+Pasukan Pengamanan Presiden (Paspampres)
+Pemerintah Provinsi DKI Jakarta
+Markas Besar POLRI
+Kementerian Pendidikan dan Kebudayaan
+Badan Siber dan Sandi Negara</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tingkat Pendidikan Terakhir</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- SD/Sederajat
+- SLTP/Sederajat
+- SLTA/Sederajat
+- Diploma I/II
+- Akademik/D3/S.Muda
+- Diploma IV/Strata I
+- Strata II
+- Strata III</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Status Pegawai</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Aktif
+- Pensiun
+- Berhenti
+- Meninggal
+- Alih Status
+- Aktif Perbantuan Setneg
+- CLTN
+- TBLN
+- Non Aktif</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Komplek</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Luar Komplek
+- Cempaka Putih (Komplek Setneg Cempaka Putih, Jakarta Pusat)
+- Sunter (Komplek Setneg Sunter Agung, Tanjung Priok, Jakarta Utara)
+- Cidodol (Komplek Setneg Cidodol, Grogol Selatan, Keb.Lama, Jakarta Selatan)
+- Ciledug (Komplek Setneg, Pd. Kacang Barat, Pd. Aren, Tangerang)
+- Suradita (Komplek Setneg, Perumahan Suradita, Cisauk, Tangerang)
+- Karawaci (Komplek Setneg, Bencongan Indah, Kelapa Dua, Tangerang)
+- Plumpang (Komplek Setneg, Tugu Utara, Koja, Jakarta Utara)
+- Jonggol (Komplek Setwapres, Perum.Griya Merselina, Desa Suka Galih, Kec. Jonggol, Kab. Bogor)
+- Cipondoh (Komplek Setneg, Panunggangan Utara, Kec. Pinang, Tangerang)</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Bulan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Januari
+- Februari
+- Maret
+- April
+- Mei
+- Juni
+- Juli
+- Agustus
+- September
+- Oktober
+- November
+- Desember</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Keterangan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Kurang
+- Sedang
+- Cukup
+- Baik
+- Sangat Baik</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Bulan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Januari
+- Februari
+- Maret
+- April
+- Mei
+- Juni
+- Juli
+- Agustus
+- September
+- Oktober
+- November
+- Desember</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Jenis Hukuman</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Teguran Lisan
+Teguran Tertulis
+Pernyataan Tidak Puas Secara Tertulis
+Penundaan Kenaikan Gaji Berkala Selama 1 (Satu) Tahun
+Penundaan Kenaikan Pangkat Selama 1 (Satu) Tahun
+Penurunan Pangkat Setingkat Lebih Rendah Selama 1 (Satu) Tahun
+Penurunan Pangkat Setingkat Lebih Rendah Selama 3 (Tiga) Tahun
+Pemindahan Dalam Rangka Penurunan Jabatan Setingkat Lebih Rendah
+Pembebasan Dari Jabatan
+Pemberhentian Dengan Hormat Tidak Atas Permintaan Sendiri Sebagai PNS
+Pemberhentian Tidak Dengan Hormat Sebagai PNS</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jenis Kelamin</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+- Laki-laki
+- Perempuan</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Agama
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>- Islam
+- Kristen
+- Katolik
+- Hindu
+- Budha
+- Konghucu</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Hubungan Keluarga</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Kepala Keluarga
+- Suami
+- Istri
+- Anak
+- Menantu
+- Cucu
+- Orang Tua
+- Mertua
+- Famili Lainnya
+- Pembantu
+- Lainnya</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Pendidikan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Tidak/Belum Sekolah
+- Belum Tamat SD/Sederajat
+- Tamat SD/Sederajat
+- SLTP/Sederajat
+- SLTA/Sederajat
+- Diploma I/II
+- Akademi/diploma III/Sarjana Muda
+- Diploma IV/Strata I
+- Strata II
+- Strata III</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Status Perkawinan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Belum Menikah
+- Menikah
+- Cerai Hidup
+- Cerai Mati</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Jenis Cuti</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Cuti Diluar Tanggungan Negara
+- Cuti Sakit
+- Cuti Besar
+- Cuti Bersalin
+- Cuti Belajar Luar Negeri
+- Cuti Tahunan Luar Negeri</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Hasil</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Kurang Memenuhi Syarat
+- Masih Memenuhi Syarat
+- Memenuhi Syarat</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments15.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Windows User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Lulus
+- Tidak Lulus</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments16.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Windows User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Kotak 1
+- Kotak 2
+- Kotak 3
+- Kotak 4
+- Kotak 5
+- Kotak 6
+- Kotak 7
+- Kotak 8
+- Kotak 9</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tingkat</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- SD/Sederajat
+- SLTP/Sederajat
+- SLTA/Sederajat
+- Diploma I/II
+- Akademik/D3/S.Muda
+- Diploma IV/Strata I
+- Strata II
+- Strata III</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Status</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Lulus
+- DO
+- Aktif
+- Non-aktif
+- Mengundurkan Diri</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Bulan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Januari
+- Februari
+- Maret
+- April
+- Mei
+- Juni
+- Juli
+- Agustus
+- September
+- Oktober
+- November
+- Desember</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Rumpun</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+- Pengelolaan Sumber Daya Manusia 
+- Kelembagaan dan Tata Laksana
+- Pengembangan Kompetensi 
+- Bantuan Hukum
+- Perencanaan Program dan Anggaran
+- Akuntabilitas Kinerja
+- Keuangan
+- Audit Internal
+- Tata Usaha
+- Arsip
+- Perpustakaan
+- Perancangan Grafis
+- Pengelolaan Bangunan
+- Pengelolaan Kendaraan serta Perlengkapan dan Peralatan
+- Kerumahtanggaan/Tata Gerha
+- Pengamanan Dalam
+- Pelayanan Medis
+- Sistem Informasi
+- Infrastruktur
+- Pengelolaan Informasi Publik
+- Peliputan dan Dokumentasi
+- Protokol VVIP dan VIP
+- Ajudan VVIP dan VIP
+- Pengelolaan Benda Seni dan Budaya
+- Pengamanan VIP dan VVIP
+- Analisis Kebijakan
+- Analisis Pengaduan Masyarakat
+- Analisis Hukum dan Perundang-undangan
+- Kerja Sama Teknik dan Tenaga Asing
+- Penetapan Pengangkatan/Pemberhentian/ Pensiun/Cuti bagi Pejabat Negara/Pejabat Pemerintah/Perwira TNI/POLRI
+- Penetapan Gelar, Tanda Jasa, dan Tanda Kehormatan
+- Perjalanan Dinas Luar Negeri</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Jenjang Jabatan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Eselon I
+- Eselon II
+- Eselon III
+- Fungsional
+- Pelaksana
+- Staf</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Keterangan Jabatan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Promosi
+- Mutasi
+- Inpassing
+- Konversi</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Bulan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Januari
+- Februari
+- Maret
+- April
+- Mei
+- Juni
+- Juli
+- Agustus
+- September
+- Oktober
+- November
+- Desember</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Golongan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Pembina Utama
+Pembina Utama Madya
+Pembina Utama Muda
+Pembina Tingkat I
+Pembina
+Penata Tingkat I
+Penata
+Penata Muda Tingkat I
+Penata Muda
+Pengatur Tingkat I
+Pengatur
+Pengatur Muda Tingkat I
+Pengatur Muda
+Juru Tingkat I
+Juru
+Juru Muda Tingkat I
+Juru Muda
+Golongan XVII
+Golongan XVI
+Golongan XV
+Golongan XIV
+Golongan XIII
+Golongan XII
+Golongan XI
+Golongan X
+Golongan IX
+Golongan VIII
+Golongan VII
+Golongan VI
+Golongan V
+Golongan IV
+Golongan III
+Golongan II
+Golongan I</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Jenis SK Golongan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Keputusan Presiden
+Keputusan Menteri Sekretaris Negara
+Keputusan Sekretaris Negara
+Keputusan Sekretaris Wakil Presiden
+Keputusan Menteri Perencanaan Pembangunan Nasional Bappenas
+Keputusan Menteri PUPR
+Keputusan Kepala Staf Angkatan Laut
+Keputusan Kepala Staf Angkatan Darat
+Surat Telegram Kapolri
+Keputusan Kepala Badan Siber dan Sandi Negara
+Keputusan Menteri Koperasi dan Usaha Kecil dan Menengah
+Keputusan Deputi Bidang Sumber Daya Manusia
+Keputusan Menteri Hukum dan HAM
+Keputusan Kepala Staf Angkatan Udara
+Keputusan Menteri PPN
+Keputusan Koordinator Bidang Pembangunan Manusia dan Kebudayaan Republik Indonesia</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Status Golongan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Aktif
+- Tidak Aktif</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Bulan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Januari
+- Februari
+- Maret
+- April
+- Mei
+- Juni
+- Juli
+- Agustus
+- September
+- Oktober
+- November
+- Desember</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Bulan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Januari
+- Februari
+- Maret
+- April
+- Mei
+- Juni
+- Juli
+- Agustus
+- September
+- Oktober
+- November
+- Desember</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Bulan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Januari
+- Februari
+- Maret
+- April
+- Mei
+- Juni
+- Juli
+- Agustus
+- September
+- Oktober
+- November
+- Desember</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Bulan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Januari
+- Februari
+- Maret
+- April
+- Mei
+- Juni
+- Juli
+- Agustus
+- September
+- Oktober
+- November
+- Desember</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Jenis SK</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Keputusan Presiden
+Keputusan Menteri Sekretaris Negara
+Keputusan Sekretaris Negara
+Keputusan Sekretaris Wakil Presiden
+Keputusan Menteri Perencanaan Pembangunan Nasional Bappenas
+Keputusan Menteri PUPR
+Keputusan Kepala Staf Angkatan Laut
+Keputusan Kepala Staf Angkatan Darat
+Surat Telegram Kapolri
+Keputusan Kepala Badan Siber dan Sandi Negara
+Keputusan Menteri Koperasi dan Usaha Kecil dan Menengah
+Keputusan Deputi Bidang Sumber Daya Manusia
+Keputusan Menteri Hukum dan HAM
+Keputusan Kepala Staf Angkatan Udara
+Keputusan Menteri PPN
+Keputusan Koordinator Bidang Pembangunan Manusia dan Kebudayaan Republik Indonesia</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Windows User</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Bulan</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Januari
+- Februari
+- Maret
+- April
+- Mei
+- Juni
+- Juli
+- Agustus
+- September
+- Oktober
+- November
+- Desember</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Periode Penilaian</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Q1
+- Q2
+- Q3
+- Q4
+- Tahunan</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Rating Perilaku Kerja</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Diatas Ekspektasi
+- Sesuai Ekspektasi
+- Dibawah Ekspektasi</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Predikat Kinerja Pegawai</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Sangat Baik
+- Baik
+- Butuh Perbaikan
+- Kurang
+- Sangat Kurang</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Capaian Kinerja Organisasi</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Sangat Baik
+- Baik
+- Cukup</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="120">
   <si>
     <t>Golongan</t>
   </si>
@@ -426,23 +2014,26 @@
     <t>Tanggal SK *</t>
   </si>
   <si>
+    <t>Tanggal Awal Hukuman Disiplin *</t>
+  </si>
+  <si>
+    <t>Tanggal Akhir Hukuman Disiplin *</t>
+  </si>
+  <si>
+    <t>Nama</t>
+  </si>
+  <si>
     <t>Jenis Perbantuan *</t>
   </si>
   <si>
     <t>Tanggal Mulai Bekerja *</t>
-  </si>
-  <si>
-    <t>Tanggal Awal Hukuman Disiplin *</t>
-  </si>
-  <si>
-    <t>Tanggal Akhir Hukuman Disiplin *</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,6 +2069,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -790,7 +2394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -804,7 +2408,8 @@
     <col min="9" max="9" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="19.28515625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="19.28515625" style="1" customWidth="1"/>
     <col min="15" max="15" width="21.5703125" style="1" customWidth="1"/>
     <col min="16" max="16" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -861,10 +2466,10 @@
         <v>66</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>86</v>
@@ -950,6 +2555,7 @@
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
     </row>
+    <row r="5" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -958,8 +2564,8 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -967,12 +2573,13 @@
     <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="24.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>89</v>
       </c>
@@ -989,38 +2596,43 @@
         <v>55</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="17.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>57</v>
       </c>
@@ -1034,37 +2646,40 @@
         <v>55</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1078,329 +2693,366 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>83</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="22.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>53</v>
+      <c r="B1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="27.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="24.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="22.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>85</v>
       </c>
@@ -1414,74 +3066,79 @@
         <v>55</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="17.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>88</v>
       </c>
@@ -1495,39 +3152,43 @@
         <v>55</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" style="1" bestFit="1" customWidth="1"/>
@@ -1541,7 +3202,7 @@
     <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>109</v>
       </c>
@@ -1568,16 +3229,20 @@
       </c>
       <c r="I1" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1590,7 +3255,7 @@
     <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>109</v>
       </c>
@@ -1617,16 +3282,21 @@
       </c>
       <c r="I1" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="54" style="1" customWidth="1"/>
@@ -1638,7 +3308,7 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>109</v>
       </c>
@@ -1659,16 +3329,20 @@
       </c>
       <c r="G1" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -1685,7 +3359,7 @@
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>97</v>
       </c>
@@ -1718,16 +3392,20 @@
       </c>
       <c r="K1" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1736,13 +3414,14 @@
     <col min="4" max="4" width="26" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="17.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>92</v>
       </c>
@@ -1762,16 +3441,20 @@
         <v>55</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/template_excel/DATA PEGAWAI NON ASN.xlsx
+++ b/public/template_excel/DATA PEGAWAI NON ASN.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
     <sheet name="Data Pegawai" sheetId="1" r:id="rId1"/>
@@ -1667,7 +1667,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="121">
   <si>
     <t>Golongan</t>
   </si>
@@ -2027,6 +2027,9 @@
   </si>
   <si>
     <t>Tanggal Mulai Bekerja *</t>
+  </si>
+  <si>
+    <t>Nama Komplek</t>
   </si>
 </sst>
 </file>
@@ -2394,7 +2397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -2424,17 +2427,18 @@
     <col min="26" max="26" width="23" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="67" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="25.28515625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="73.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="58.28515625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="25.28515625" style="1" customWidth="1"/>
+    <col min="38" max="38" width="73.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>60</v>
       </c>
@@ -2523,39 +2527,42 @@
         <v>75</v>
       </c>
       <c r="AD1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="AI2" s="4"/>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="AJ2" s="4"/>
+      <c r="AK2" s="4"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="AI3" s="4"/>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="AJ3" s="4"/>
+      <c r="AK3" s="4"/>
     </row>
-    <row r="5" spans="1:37" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/public/template_excel/DATA PEGAWAI NON ASN.xlsx
+++ b/public/template_excel/DATA PEGAWAI NON ASN.xlsx
@@ -372,7 +372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -404,7 +404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AG1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1667,7 +1667,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="125">
   <si>
     <t>Golongan</t>
   </si>
@@ -2030,6 +2030,18 @@
   </si>
   <si>
     <t>Nama Komplek</t>
+  </si>
+  <si>
+    <t>Masa Kerja Keseluruhan Jumlah Tahun</t>
+  </si>
+  <si>
+    <t>Masa Kerja Keseluruhan Jumlah Bulan</t>
+  </si>
+  <si>
+    <t>Masa Kerja Golongan Jumlah Tahun</t>
+  </si>
+  <si>
+    <t>Masa Kerja Golongan Jumlah Bulan</t>
   </si>
 </sst>
 </file>
@@ -2397,7 +2409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AP5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -2423,22 +2435,26 @@
     <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="58.28515625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="67" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="25.28515625" style="1" customWidth="1"/>
-    <col min="38" max="38" width="73.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="25" max="25" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="39" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="36.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="36.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="58.28515625" style="1" customWidth="1"/>
+    <col min="35" max="35" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="25.28515625" style="1" customWidth="1"/>
+    <col min="42" max="42" width="73.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>60</v>
       </c>
@@ -2512,57 +2528,65 @@
         <v>54</v>
       </c>
       <c r="Y1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="AJ2" s="4"/>
-      <c r="AK2" s="4"/>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="AJ3" s="4"/>
-      <c r="AK3" s="4"/>
-    </row>
-    <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/public/template_excel/DATA PEGAWAI NON ASN.xlsx
+++ b/public/template_excel/DATA PEGAWAI NON ASN.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" firstSheet="10" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="Data Pegawai" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
     <sheet name="Riwayat Keluarga" sheetId="13" r:id="rId12"/>
     <sheet name="Riwayat Cuti" sheetId="14" r:id="rId13"/>
     <sheet name="Riwayat Catatan" sheetId="15" r:id="rId14"/>
-    <sheet name="Hasil Assessment" sheetId="16" r:id="rId15"/>
-    <sheet name="Hasil Uji Kompetensi" sheetId="17" r:id="rId16"/>
-    <sheet name="Hasil Talent Pool" sheetId="18" r:id="rId17"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -372,7 +369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -401,39 +398,6 @@
 - CLTN
 - TBLN
 - Non Aktif</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Komplek</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-- Luar Komplek
-- Cempaka Putih (Komplek Setneg Cempaka Putih, Jakarta Pusat)
-- Sunter (Komplek Setneg Sunter Agung, Tanjung Priok, Jakarta Utara)
-- Cidodol (Komplek Setneg Cidodol, Grogol Selatan, Keb.Lama, Jakarta Selatan)
-- Ciledug (Komplek Setneg, Pd. Kacang Barat, Pd. Aren, Tangerang)
-- Suradita (Komplek Setneg, Perumahan Suradita, Cisauk, Tangerang)
-- Karawaci (Komplek Setneg, Bencongan Indah, Kelapa Dua, Tangerang)
-- Plumpang (Komplek Setneg, Tugu Utara, Koja, Jakarta Utara)
-- Jonggol (Komplek Setwapres, Perum.Griya Merselina, Desa Suka Galih, Kec. Jonggol, Kab. Bogor)
-- Cipondoh (Komplek Setneg, Panunggangan Utara, Kec. Pinang, Tangerang)</t>
         </r>
       </text>
     </comment>
@@ -790,119 +754,6 @@
 </comments>
 </file>
 
-<file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Windows User</author>
-  </authors>
-  <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Hasil</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-- Kurang Memenuhi Syarat
-- Masih Memenuhi Syarat
-- Memenuhi Syarat</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments15.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Windows User</author>
-  </authors>
-  <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Windows User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-- Lulus
-- Tidak Lulus</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments16.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Windows User</author>
-  </authors>
-  <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Windows User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-- Kotak 1
-- Kotak 2
-- Kotak 3
-- Kotak 4
-- Kotak 5
-- Kotak 6
-- Kotak 7
-- Kotak 8
-- Kotak 9</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -1010,61 +861,6 @@
 - Oktober
 - November
 - Desember</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Rumpun</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-- Pengelolaan Sumber Daya Manusia 
-- Kelembagaan dan Tata Laksana
-- Pengembangan Kompetensi 
-- Bantuan Hukum
-- Perencanaan Program dan Anggaran
-- Akuntabilitas Kinerja
-- Keuangan
-- Audit Internal
-- Tata Usaha
-- Arsip
-- Perpustakaan
-- Perancangan Grafis
-- Pengelolaan Bangunan
-- Pengelolaan Kendaraan serta Perlengkapan dan Peralatan
-- Kerumahtanggaan/Tata Gerha
-- Pengamanan Dalam
-- Pelayanan Medis
-- Sistem Informasi
-- Infrastruktur
-- Pengelolaan Informasi Publik
-- Peliputan dan Dokumentasi
-- Protokol VVIP dan VIP
-- Ajudan VVIP dan VIP
-- Pengelolaan Benda Seni dan Budaya
-- Pengamanan VIP dan VVIP
-- Analisis Kebijakan
-- Analisis Pengaduan Masyarakat
-- Analisis Hukum dan Perundang-undangan
-- Kerja Sama Teknik dan Tenaga Asing
-- Penetapan Pengangkatan/Pemberhentian/ Pensiun/Cuti bagi Pejabat Negara/Pejabat Pemerintah/Perwira TNI/POLRI
-- Penetapan Gelar, Tanda Jasa, dan Tanda Kehormatan
-- Perjalanan Dinas Luar Negeri</t>
         </r>
       </text>
     </comment>
@@ -1667,7 +1463,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
   <si>
     <t>Golongan</t>
   </si>
@@ -1705,9 +1501,6 @@
     <t>Tahun</t>
   </si>
   <si>
-    <t>No Karpeg</t>
-  </si>
-  <si>
     <t>NPWP</t>
   </si>
   <si>
@@ -1726,9 +1519,6 @@
     <t>No Telepon Kantor</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
     <t>Keterangan Sekolah</t>
   </si>
   <si>
@@ -1831,9 +1621,6 @@
     <t>Urut Keluarga</t>
   </si>
   <si>
-    <t>No Karisu</t>
-  </si>
-  <si>
     <t>NIK *</t>
   </si>
   <si>
@@ -1876,27 +1663,12 @@
     <t>TMT Golongan *</t>
   </si>
   <si>
-    <t>Instansi Induk *</t>
-  </si>
-  <si>
     <t>Tingkat *</t>
   </si>
   <si>
-    <t>Nama Sekolah/Universitas *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tahun Lulus * </t>
-  </si>
-  <si>
-    <t>Status Pegawai *</t>
-  </si>
-  <si>
     <t>No NIK *</t>
   </si>
   <si>
-    <t>Komplek *</t>
-  </si>
-  <si>
     <t>Nama Sekolah *</t>
   </si>
   <si>
@@ -1921,9 +1693,6 @@
     <t>Catatan *</t>
   </si>
   <si>
-    <t>Hasil *</t>
-  </si>
-  <si>
     <t>Nama Riwayat Jabatan *</t>
   </si>
   <si>
@@ -1963,18 +1732,9 @@
     <t>Nama Penghargaan *</t>
   </si>
   <si>
-    <t>Kontak Darurat (Nama, Nomor Handphone, Hubungan dengan pegawai) *</t>
-  </si>
-  <si>
-    <t>No KK *</t>
-  </si>
-  <si>
     <t>Eselon</t>
   </si>
   <si>
-    <t>Tingkat Pendidikan Terakhir*</t>
-  </si>
-  <si>
     <t>Email Dinas</t>
   </si>
   <si>
@@ -1993,9 +1753,6 @@
     <t>Keterangan *</t>
   </si>
   <si>
-    <t>Tanggal *</t>
-  </si>
-  <si>
     <t>Nama Diklat *</t>
   </si>
   <si>
@@ -2023,32 +1780,50 @@
     <t>Nama</t>
   </si>
   <si>
-    <t>Jenis Perbantuan *</t>
-  </si>
-  <si>
-    <t>Tanggal Mulai Bekerja *</t>
-  </si>
-  <si>
-    <t>Nama Komplek</t>
-  </si>
-  <si>
-    <t>Masa Kerja Keseluruhan Jumlah Tahun</t>
-  </si>
-  <si>
-    <t>Masa Kerja Keseluruhan Jumlah Bulan</t>
-  </si>
-  <si>
-    <t>Masa Kerja Golongan Jumlah Tahun</t>
-  </si>
-  <si>
-    <t>Masa Kerja Golongan Jumlah Bulan</t>
+    <t>Status Perkawinan</t>
+  </si>
+  <si>
+    <t>Jenis Perbantuan</t>
+  </si>
+  <si>
+    <t>Tanggal Mulai Bekerja di Sekretariat Wakil Presiden</t>
+  </si>
+  <si>
+    <t>TMT Golongan</t>
+  </si>
+  <si>
+    <t>Instansi Induk</t>
+  </si>
+  <si>
+    <t>Tingkat Pendidikan Akhir</t>
+  </si>
+  <si>
+    <t>Nama Sekolah/Universitas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tahun Lulus </t>
+  </si>
+  <si>
+    <t>Status Pegawai</t>
+  </si>
+  <si>
+    <t>No KK</t>
+  </si>
+  <si>
+    <t>Alamat Sesuai KTP</t>
+  </si>
+  <si>
+    <t>Email *</t>
+  </si>
+  <si>
+    <t>Kontak Darurat (Nama, Nomor Handphone, Hubungan dengan pegawai)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2060,14 +1835,6 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2116,21 +1883,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2409,7 +2173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AP5"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -2434,17 +2198,17 @@
     <col min="21" max="21" width="29" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="39" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="36.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="36.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="58.28515625" style="1" customWidth="1"/>
-    <col min="35" max="35" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="73.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -2454,9 +2218,9 @@
     <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>7</v>
@@ -2465,128 +2229,103 @@
         <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="W1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AN1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO1" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AP1" s="2" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="AN3" s="4"/>
-      <c r="AO3" s="4"/>
-    </row>
-    <row r="5" spans="1:42" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2612,28 +2351,28 @@
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2644,7 +2383,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -2665,19 +2404,19 @@
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>0</v>
@@ -2686,45 +2425,29 @@
         <v>9</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2759,58 +2482,58 @@
   <sheetData>
     <row r="1" spans="1:18" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="N1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2838,25 +2561,25 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2878,128 +2601,17 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3022,16 +2634,16 @@
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -3040,13 +2652,13 @@
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3085,61 +2697,61 @@
   <sheetData>
     <row r="1" spans="1:19" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -3171,25 +2783,25 @@
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>4</v>
@@ -3201,13 +2813,13 @@
         <v>6</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -3235,34 +2847,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3288,34 +2900,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3341,28 +2953,28 @@
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3392,40 +3004,40 @@
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3454,34 +3066,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/public/template_excel/DATA PEGAWAI NON ASN.xlsx
+++ b/public/template_excel/DATA PEGAWAI NON ASN.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
     <sheet name="Data Pegawai" sheetId="1" r:id="rId1"/>
@@ -617,9 +617,6 @@
     <t>Status Perkawinan</t>
   </si>
   <si>
-    <t>Jenis Perbantuan</t>
-  </si>
-  <si>
     <t>Tanggal Mulai Bekerja di Sekretariat Wakil Presiden</t>
   </si>
   <si>
@@ -629,18 +626,12 @@
     <t>Instansi Induk</t>
   </si>
   <si>
-    <t>Tingkat Pendidikan Akhir</t>
-  </si>
-  <si>
     <t>Nama Sekolah/Universitas</t>
   </si>
   <si>
     <t xml:space="preserve">Tahun Lulus </t>
   </si>
   <si>
-    <t>Status Pegawai</t>
-  </si>
-  <si>
     <t>No KK</t>
   </si>
   <si>
@@ -650,7 +641,16 @@
     <t>Email *</t>
   </si>
   <si>
-    <t>Kontak Darurat (Nama, Nomor Handphone, Hubungan dengan pegawai)</t>
+    <t>Jenis Perbantuan *</t>
+  </si>
+  <si>
+    <t>Tingkat Pendidikan Akhir *</t>
+  </si>
+  <si>
+    <t>Status Pegawai *</t>
+  </si>
+  <si>
+    <t>Kontak Darurat (Nama, Nomor Handphone, Hubungan dengan pegawai) *</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1020,7 @@
     <col min="9" max="9" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="53" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="19.28515625" style="1" customWidth="1"/>
     <col min="15" max="15" width="21.5703125" style="1" customWidth="1"/>
     <col min="16" max="16" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1083,10 +1083,10 @@
         <v>39</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>34</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>36</v>
@@ -1107,25 +1107,25 @@
         <v>4</v>
       </c>
       <c r="S1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="U1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="W1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>32</v>
@@ -1134,7 +1134,7 @@
         <v>6</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AC1" s="2" t="s">
         <v>7</v>
@@ -1149,7 +1149,7 @@
         <v>10</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AH1" s="2" t="s">
         <v>37</v>

--- a/public/template_excel/DATA PEGAWAI NON ASN.xlsx
+++ b/public/template_excel/DATA PEGAWAI NON ASN.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\WORK\simdatuk-dev\public\template_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\api\public\template_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2513488-A197-45C5-8D5D-20EF6950CA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Pegawai" sheetId="1" r:id="rId1"/>
@@ -25,12 +26,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Windows User</author>
   </authors>
   <commentList>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -59,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -84,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -112,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -151,7 +152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -181,7 +182,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -239,7 +240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -276,7 +277,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -326,7 +327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -357,7 +358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -394,12 +395,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Windows User</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -434,7 +435,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -463,7 +464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -495,7 +496,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Golongan</t>
   </si>
@@ -569,12 +570,6 @@
     <t>NIK *</t>
   </si>
   <si>
-    <t>Bulan Periode Input Riwayat *</t>
-  </si>
-  <si>
-    <t>Tahun Periode Input Riwayat *</t>
-  </si>
-  <si>
     <t>Nama *</t>
   </si>
   <si>
@@ -596,9 +591,6 @@
     <t>No NIK *</t>
   </si>
   <si>
-    <t>Nama Riwayat Jabatan *</t>
-  </si>
-  <si>
     <t>Jabatan *</t>
   </si>
   <si>
@@ -651,12 +643,27 @@
   </si>
   <si>
     <t>Kontak Darurat (Nama, Nomor Handphone, Hubungan dengan pegawai) *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nama Riwayat Jabatan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulan Periode Input Riwayat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tahun Periode Input Riwayat </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabatan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMT Menjabat </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1005,55 +1012,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AI3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="53" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="19.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="21.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="33.140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="30.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="19.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="21.5546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="33.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="30.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="58.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="27.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="73.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="73.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="25.28515625" style="1" customWidth="1"/>
-    <col min="42" max="42" width="73.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="37" max="37" width="7.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="25.33203125" style="1" customWidth="1"/>
+    <col min="42" max="42" width="73.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
@@ -1062,79 +1069,79 @@
         <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="N1" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="W1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AC1" s="2" t="s">
         <v>7</v>
@@ -1149,16 +1156,16 @@
         <v>10</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1167,50 +1174,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="27.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>11</v>
@@ -1222,7 +1229,7 @@
         <v>13</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>

--- a/public/template_excel/DATA PEGAWAI NON ASN.xlsx
+++ b/public/template_excel/DATA PEGAWAI NON ASN.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\api\public\template_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\simdatuk-dev\public\template_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2513488-A197-45C5-8D5D-20EF6950CA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data Pegawai" sheetId="1" r:id="rId1"/>
@@ -26,12 +25,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Windows User</author>
   </authors>
   <commentList>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -113,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -152,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -182,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -240,7 +239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -277,7 +276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -327,7 +326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -358,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -395,12 +394,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Windows User</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -435,7 +434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -458,13 +457,14 @@
 - Eselon I
 - Eselon II
 - Eselon III
+- Eselon IV
+- Pelaksana
 - Fungsional
-- Pelaksana
 - Staf</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -663,7 +663,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1012,53 +1012,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AI3"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="53" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="19.33203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="21.5546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="33.109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="30.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="19.36328125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="21.54296875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="17.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="33.08984375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="30.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="58.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="27.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="17.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="58.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="27.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="73.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="73.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="7.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="25.33203125" style="1" customWidth="1"/>
-    <col min="42" max="42" width="73.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.109375" style="1"/>
+    <col min="37" max="37" width="7.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="25.36328125" style="1" customWidth="1"/>
+    <col min="42" max="42" width="73.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1174,33 +1174,33 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S1"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.08984375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.109375" style="1"/>
+    <col min="17" max="17" width="15.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>49</v>
       </c>

--- a/public/template_excel/DATA PEGAWAI NON ASN.xlsx
+++ b/public/template_excel/DATA PEGAWAI NON ASN.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12460"/>
   </bookViews>
   <sheets>
     <sheet name="Data Pegawai" sheetId="1" r:id="rId1"/>
@@ -657,7 +657,7 @@
     <t xml:space="preserve">Jabatan </t>
   </si>
   <si>
-    <t xml:space="preserve">TMT Menjabat </t>
+    <t xml:space="preserve">TMT Jabatan </t>
   </si>
 </sst>
 </file>

--- a/public/template_excel/DATA PEGAWAI NON ASN.xlsx
+++ b/public/template_excel/DATA PEGAWAI NON ASN.xlsx
@@ -630,9 +630,6 @@
     <t>Alamat Sesuai KTP</t>
   </si>
   <si>
-    <t>Email *</t>
-  </si>
-  <si>
     <t>Jenis Perbantuan *</t>
   </si>
   <si>
@@ -658,6 +655,9 @@
   </si>
   <si>
     <t xml:space="preserve">TMT Jabatan </t>
+  </si>
+  <si>
+    <t>Email</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1090,7 @@
         <v>36</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>37</v>
@@ -1117,7 +1117,7 @@
         <v>39</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U1" s="2" t="s">
         <v>40</v>
@@ -1129,7 +1129,7 @@
         <v>5</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y1" s="2" t="s">
         <v>42</v>
@@ -1156,13 +1156,13 @@
         <v>10</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AH1" s="2" t="s">
         <v>34</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -1202,13 +1202,13 @@
   <sheetData>
     <row r="1" spans="1:19" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>23</v>
@@ -1217,7 +1217,7 @@
         <v>35</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>11</v>
@@ -1229,7 +1229,7 @@
         <v>13</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
